--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c5fac51d00441d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcbf238436f8743c0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcbf238436f8743c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bb359dd3f95402e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6bb359dd3f95402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R253f9f20acf843b6"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R253f9f20acf843b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc75cd7d7d961478b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc75cd7d7d961478b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c794472d14b4706"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8c794472d14b4706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42a2a5e08f5e4e36"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R42a2a5e08f5e4e36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb813b418274f4c26"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb813b418274f4c26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R197d114c4ef9487a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R197d114c4ef9487a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rebd016d67a4d43c8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rebd016d67a4d43c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7088444d367f4ce1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7088444d367f4ce1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R76b2a9ecc35f4250"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R76b2a9ecc35f4250"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd24c4b9946db400f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd24c4b9946db400f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd83de10a127540e9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd83de10a127540e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R009062149c1b446d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/SheetProtectionWithPassword/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R009062149c1b446d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc2193b30c4d54e09"/>
   </x:sheets>
 </x:workbook>
 </file>
